--- a/AtchisonRegime/Outputs/UK/df_regCLI_UK.xlsx
+++ b/AtchisonRegime/Outputs/UK/df_regCLI_UK.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H774"/>
+  <dimension ref="A1:H775"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20293,22 +20293,22 @@
         <v>45443</v>
       </c>
       <c r="B764" t="n">
-        <v>101</v>
+        <v>100.969</v>
       </c>
       <c r="C764" t="n">
-        <v>100.81</v>
+        <v>100.7996666666667</v>
       </c>
       <c r="D764" t="n">
-        <v>98.87222222222222</v>
+        <v>98.87136111111111</v>
       </c>
       <c r="E764" t="n">
-        <v>2.248181628543429</v>
+        <v>2.247349132425894</v>
       </c>
       <c r="F764" t="b">
         <v>1</v>
       </c>
       <c r="G764" t="n">
-        <v>0.09340882308341358</v>
+        <v>0.07964939555553918</v>
       </c>
       <c r="H764" t="b">
         <v>1</v>
@@ -20319,22 +20319,22 @@
         <v>45473</v>
       </c>
       <c r="B765" t="n">
-        <v>101.2</v>
+        <v>101.1814</v>
       </c>
       <c r="C765" t="n">
-        <v>100.9966666666667</v>
+        <v>100.9801333333333</v>
       </c>
       <c r="D765" t="n">
-        <v>98.84999999999999</v>
+        <v>98.84862222222222</v>
       </c>
       <c r="E765" t="n">
-        <v>2.220160869332182</v>
+        <v>2.218748158130141</v>
       </c>
       <c r="F765" t="b">
         <v>1</v>
       </c>
       <c r="G765" t="n">
-        <v>0.0900835623051776</v>
+        <v>0.09572965693366631</v>
       </c>
       <c r="H765" t="b">
         <v>1</v>
@@ -20345,22 +20345,22 @@
         <v>45504</v>
       </c>
       <c r="B766" t="n">
-        <v>101.35</v>
+        <v>101.3378</v>
       </c>
       <c r="C766" t="n">
-        <v>101.1833333333333</v>
+        <v>101.1627333333333</v>
       </c>
       <c r="D766" t="n">
-        <v>98.82805555555557</v>
+        <v>98.8263388888889</v>
       </c>
       <c r="E766" t="n">
-        <v>2.190417858954071</v>
+        <v>2.188570840039808</v>
       </c>
       <c r="F766" t="b">
         <v>1</v>
       </c>
       <c r="G766" t="n">
-        <v>0.06848008446736131</v>
+        <v>0.07146216020915283</v>
       </c>
       <c r="H766" t="b">
         <v>1</v>
@@ -20371,22 +20371,22 @@
         <v>45535</v>
       </c>
       <c r="B767" t="n">
-        <v>101.39</v>
+        <v>101.3868</v>
       </c>
       <c r="C767" t="n">
-        <v>101.3133333333333</v>
+        <v>101.302</v>
       </c>
       <c r="D767" t="n">
-        <v>98.80833333333334</v>
+        <v>98.80652777777777</v>
       </c>
       <c r="E767" t="n">
-        <v>2.163142555238847</v>
+        <v>2.161146891366486</v>
       </c>
       <c r="F767" t="b">
         <v>1</v>
       </c>
       <c r="G767" t="n">
-        <v>0.01849161531362393</v>
+        <v>0.02267314646484296</v>
       </c>
       <c r="H767" t="b">
         <v>1</v>
@@ -20397,22 +20397,22 @@
         <v>45565</v>
       </c>
       <c r="B768" t="n">
-        <v>101.33</v>
+        <v>101.3348</v>
       </c>
       <c r="C768" t="n">
-        <v>101.3566666666667</v>
+        <v>101.3531333333333</v>
       </c>
       <c r="D768" t="n">
-        <v>98.79166666666667</v>
+        <v>98.78999444444445</v>
       </c>
       <c r="E768" t="n">
-        <v>2.140597379905122</v>
+        <v>2.138729242723834</v>
       </c>
       <c r="F768" t="b">
         <v>0</v>
       </c>
       <c r="G768" t="n">
-        <v>-0.02802955874058935</v>
+        <v>-0.02431350306585164</v>
       </c>
       <c r="H768" t="b">
         <v>1</v>
@@ -20423,22 +20423,22 @@
         <v>45596</v>
       </c>
       <c r="B769" t="n">
-        <v>101.23</v>
+        <v>101.2447</v>
       </c>
       <c r="C769" t="n">
-        <v>101.3166666666667</v>
+        <v>101.3221</v>
       </c>
       <c r="D769" t="n">
-        <v>98.77916666666667</v>
+        <v>98.77790277777778</v>
       </c>
       <c r="E769" t="n">
-        <v>2.124502462762809</v>
+        <v>2.123096665787335</v>
       </c>
       <c r="F769" t="b">
         <v>0</v>
       </c>
       <c r="G769" t="n">
-        <v>-0.04706984423541187</v>
+        <v>-0.04243801116167915</v>
       </c>
       <c r="H769" t="b">
         <v>1</v>
@@ -20449,22 +20449,22 @@
         <v>45626</v>
       </c>
       <c r="B770" t="n">
-        <v>101.14</v>
+        <v>101.1665</v>
       </c>
       <c r="C770" t="n">
-        <v>101.2333333333333</v>
+        <v>101.2486666666667</v>
       </c>
       <c r="D770" t="n">
-        <v>98.77388888888888</v>
+        <v>98.77336111111111</v>
       </c>
       <c r="E770" t="n">
-        <v>2.118211209997307</v>
+        <v>2.117649200178206</v>
       </c>
       <c r="F770" t="b">
         <v>0</v>
       </c>
       <c r="G770" t="n">
-        <v>-0.04248868081484558</v>
+        <v>-0.03692774043661936</v>
       </c>
       <c r="H770" t="b">
         <v>0</v>
@@ -20475,22 +20475,22 @@
         <v>45657</v>
       </c>
       <c r="B771" t="n">
-        <v>101.09</v>
+        <v>101.1211</v>
       </c>
       <c r="C771" t="n">
-        <v>101.1533333333334</v>
+        <v>101.1774333333333</v>
       </c>
       <c r="D771" t="n">
-        <v>98.7813888888889</v>
+        <v>98.78172499999999</v>
       </c>
       <c r="E771" t="n">
-        <v>2.126126125512508</v>
+        <v>2.12653953312138</v>
       </c>
       <c r="F771" t="b">
         <v>0</v>
       </c>
       <c r="G771" t="n">
-        <v>-0.02351694915932823</v>
+        <v>-0.02134923865410661</v>
       </c>
       <c r="H771" t="b">
         <v>0</v>
@@ -20501,22 +20501,22 @@
         <v>45688</v>
       </c>
       <c r="B772" t="n">
-        <v>101.11</v>
+        <v>101.1218</v>
       </c>
       <c r="C772" t="n">
-        <v>101.1133333333333</v>
+        <v>101.1364666666667</v>
       </c>
       <c r="D772" t="n">
-        <v>98.8088888888889</v>
+        <v>98.80955277777778</v>
       </c>
       <c r="E772" t="n">
-        <v>2.150201024193779</v>
+        <v>2.150966936517526</v>
       </c>
       <c r="F772" t="b">
         <v>1</v>
       </c>
       <c r="G772" t="n">
-        <v>0.009301455898754887</v>
+        <v>0.0003254350348723328</v>
       </c>
       <c r="H772" t="b">
         <v>0</v>
@@ -20527,22 +20527,22 @@
         <v>45716</v>
       </c>
       <c r="B773" t="n">
-        <v>101.19</v>
+        <v>101.1619</v>
       </c>
       <c r="C773" t="n">
-        <v>101.13</v>
+        <v>101.1349333333333</v>
       </c>
       <c r="D773" t="n">
-        <v>98.86277777777779</v>
+        <v>98.86266111111111</v>
       </c>
       <c r="E773" t="n">
-        <v>2.185591271566746</v>
+        <v>2.185478453961442</v>
       </c>
       <c r="F773" t="b">
         <v>1</v>
       </c>
       <c r="G773" t="n">
-        <v>0.03660336726301534</v>
+        <v>0.01834838496226009</v>
       </c>
       <c r="H773" t="b">
         <v>0</v>
@@ -20553,24 +20553,50 @@
         <v>45747</v>
       </c>
       <c r="B774" t="n">
-        <v>101.29</v>
+        <v>101.1632</v>
       </c>
       <c r="C774" t="n">
-        <v>101.1966666666667</v>
+        <v>101.1489666666667</v>
       </c>
       <c r="D774" t="n">
-        <v>98.94527777777779</v>
+        <v>98.94163888888889</v>
       </c>
       <c r="E774" t="n">
-        <v>2.220296616105968</v>
+        <v>2.216461214417122</v>
       </c>
       <c r="F774" t="b">
         <v>1</v>
       </c>
       <c r="G774" t="n">
-        <v>0.04503902734193773</v>
+        <v>0.0005865205272010107</v>
       </c>
       <c r="H774" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B775" t="n">
+        <v>101.1131</v>
+      </c>
+      <c r="C775" t="n">
+        <v>101.1460666666667</v>
+      </c>
+      <c r="D775" t="n">
+        <v>99.04311388888888</v>
+      </c>
+      <c r="E775" t="n">
+        <v>2.230270978174373</v>
+      </c>
+      <c r="F775" t="b">
+        <v>0</v>
+      </c>
+      <c r="G775" t="n">
+        <v>-0.02246363804680394</v>
+      </c>
+      <c r="H775" t="b">
         <v>1</v>
       </c>
     </row>
